--- a/Result/profitability/2901.xlsx
+++ b/Result/profitability/2901.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
         <v>0.0975</v>
       </c>
       <c r="N2" t="n">
-        <v>77.28375</v>
+        <v>77.35375000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09</v>
+        <v>0.0925</v>
       </c>
       <c r="N3" t="n">
-        <v>68.72750000000001</v>
+        <v>68.71124999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08875000000000001</v>
+        <v>0.0925</v>
       </c>
       <c r="N4" t="n">
-        <v>59.82749999999999</v>
+        <v>60.13625</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.09</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09</v>
+        <v>0.09375</v>
       </c>
       <c r="N5" t="n">
-        <v>51.53</v>
+        <v>51.72875000000001</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08875</v>
+        <v>0.09125</v>
       </c>
       <c r="N6" t="n">
-        <v>43.00749999999999</v>
+        <v>43.0925</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.05</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08375</v>
+        <v>0.08125</v>
       </c>
       <c r="N7" t="n">
-        <v>34.48625</v>
+        <v>34.75624999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0.07625000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>26.01625</v>
+        <v>25.99875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.11</v>
       </c>
       <c r="M9" t="n">
-        <v>0.07625000000000001</v>
+        <v>0.07625</v>
       </c>
       <c r="N9" t="n">
         <v>17.22375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2901</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>33</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4</v>
+      </c>
+      <c r="E75" t="n">
+        <v>28</v>
+      </c>
+      <c r="F75" t="n">
+        <v>86.93000000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>16.14%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>10</v>
+      </c>
+      <c r="K75" t="n">
+        <v>8</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N75" t="n">
+        <v>86.03125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.1399999999999864</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.001607901688296609</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.590000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.01863135692524032</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
